--- a/Model objective analysis/Capacity increase/L shape min unvax 35 scenarios/L_Shape_min_unvax_35_tender_fixed.xlsx
+++ b/Model objective analysis/Capacity increase/L shape min unvax 35 scenarios/L_Shape_min_unvax_35_tender_fixed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,7 +452,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -460,10 +460,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -473,7 +473,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -481,10 +481,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -494,7 +494,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -502,10 +502,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -515,7 +515,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -536,7 +536,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -544,10 +544,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -557,18 +557,18 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PCV</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -578,18 +578,18 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PCV</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -599,18 +599,18 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PCV</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -620,18 +620,18 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PCV</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -641,18 +641,18 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PCV</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -670,10 +670,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -683,18 +683,18 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>Mumps</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -704,18 +704,18 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>Mumps</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -725,18 +725,18 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>Mumps</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -775,10 +775,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -788,15 +788,15 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mumps</t>
+          <t>HPV</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
         <v>10</v>
@@ -809,18 +809,18 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mumps</t>
+          <t>HPV</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -830,18 +830,18 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mumps</t>
+          <t>HPV</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -851,18 +851,18 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HPV</t>
+          <t>Hib</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -872,18 +872,18 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>135</v>
+        <v>181</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HPV</t>
+          <t>Hib</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -893,18 +893,18 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HPV</t>
+          <t>Hib</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -914,18 +914,18 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>148</v>
+        <v>201</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HPV</t>
+          <t>Pertussis</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -935,18 +935,18 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>155</v>
+        <v>216</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HPV</t>
+          <t>Pertussis</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -956,18 +956,18 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>169</v>
+        <v>220</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hib</t>
+          <t>Pertussis</t>
         </is>
       </c>
       <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
         <v>4</v>
-      </c>
-      <c r="D26" t="n">
-        <v>8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -977,18 +977,18 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>179</v>
+        <v>239</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hib</t>
+          <t>Pertussis</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -998,18 +998,18 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>185</v>
+        <v>249</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hib</t>
+          <t>Rotavirus</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1019,18 +1019,18 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>191</v>
+        <v>253</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hib</t>
+          <t>Rotavirus</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1040,18 +1040,18 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>199</v>
+        <v>256</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hib</t>
+          <t>Rotavirus</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1061,18 +1061,18 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pertussis</t>
+          <t>Rotavirus</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1082,18 +1082,18 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>218</v>
+        <v>279</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pertussis</t>
+          <t>Rotavirus</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1103,18 +1103,18 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>222</v>
+        <v>288</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pertussis</t>
+          <t>Polio</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1124,15 +1124,15 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>225</v>
+        <v>296</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pertussis</t>
+          <t>Polio</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D34" t="n">
         <v>10</v>
@@ -1145,18 +1145,18 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>233</v>
+        <v>300</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pertussis</t>
+          <t>Polio</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1166,18 +1166,18 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>239</v>
+        <v>304</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pertussis</t>
+          <t>Polio</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1187,18 +1187,18 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>241</v>
+        <v>313</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Rotavirus</t>
+          <t>Polio</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1208,18 +1208,18 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>249</v>
+        <v>319</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Rotavirus</t>
+          <t>Polio</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1229,18 +1229,18 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>260</v>
+        <v>336</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Rotavirus</t>
+          <t>Diphtheria</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1250,18 +1250,18 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>265</v>
+        <v>341</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Rotavirus</t>
+          <t>Diphtheria</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1271,18 +1271,18 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>267</v>
+        <v>359</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Rotavirus</t>
+          <t>Diphtheria</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1292,18 +1292,18 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>273</v>
+        <v>361</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Rotavirus</t>
+          <t>Hepatitis_B</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1313,18 +1313,18 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>279</v>
+        <v>376</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Rotavirus</t>
+          <t>Hepatitis_B</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1334,18 +1334,18 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>289</v>
+        <v>380</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Polio</t>
+          <t>Hepatitis_B</t>
         </is>
       </c>
       <c r="C44" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" t="n">
         <v>4</v>
-      </c>
-      <c r="D44" t="n">
-        <v>8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1355,18 +1355,18 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>298</v>
+        <v>399</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Polio</t>
+          <t>Hepatitis_B</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1376,18 +1376,18 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>299</v>
+        <v>416</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Polio</t>
+          <t>Tetanus</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1397,18 +1397,18 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>304</v>
+        <v>421</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Polio</t>
+          <t>Tetanus</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1418,18 +1418,18 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>306</v>
+        <v>439</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Polio</t>
+          <t>Tetanus</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1439,18 +1439,18 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>309</v>
+        <v>447</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Polio</t>
+          <t>Rubella</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1460,18 +1460,18 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>319</v>
+        <v>452</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Polio</t>
+          <t>Rubella</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1481,18 +1481,18 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>331</v>
+        <v>457</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Diphtheria</t>
+          <t>Rubella</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D51" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -1502,18 +1502,18 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>337</v>
+        <v>460</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Diphtheria</t>
+          <t>Rubella</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -1523,356 +1523,20 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>339</v>
+        <v>478</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Diphtheria</t>
+          <t>Rubella</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E53" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="n">
-        <v>344</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>10</v>
-      </c>
-      <c r="D54" t="n">
-        <v>10</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="n">
-        <v>346</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>9</v>
-      </c>
-      <c r="D55" t="n">
-        <v>9</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="n">
-        <v>359</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="n">
-        <v>369</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Hepatitis_B</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>4</v>
-      </c>
-      <c r="D57" t="n">
-        <v>8</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="n">
-        <v>379</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Hepatitis_B</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>2</v>
-      </c>
-      <c r="D58" t="n">
-        <v>5</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="n">
-        <v>385</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Hepatitis_B</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>9</v>
-      </c>
-      <c r="D59" t="n">
-        <v>10</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="n">
-        <v>399</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Hepatitis_B</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="n">
-        <v>408</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>4</v>
-      </c>
-      <c r="D61" t="n">
-        <v>7</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="n">
-        <v>419</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>2</v>
-      </c>
-      <c r="D62" t="n">
-        <v>5</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="n">
-        <v>425</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>9</v>
-      </c>
-      <c r="D63" t="n">
-        <v>10</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="n">
-        <v>428</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>8</v>
-      </c>
-      <c r="D64" t="n">
-        <v>9</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="1" t="n">
-        <v>439</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="1" t="n">
-        <v>443</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>5</v>
-      </c>
-      <c r="D66" t="n">
-        <v>9</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="1" t="n">
-        <v>452</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>6</v>
-      </c>
-      <c r="D67" t="n">
-        <v>10</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="n">
-        <v>461</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>2</v>
-      </c>
-      <c r="D68" t="n">
-        <v>6</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="1" t="n">
-        <v>478</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>1</v>
-      </c>
-      <c r="D69" t="n">
-        <v>3</v>
-      </c>
-      <c r="E69" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
